--- a/artfynd/A 59457-2023 artfynd.xlsx
+++ b/artfynd/A 59457-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59457-2023 artfynd.xlsx
+++ b/artfynd/A 59457-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74209838</v>
       </c>
       <c r="B2" t="n">
-        <v>96926</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546835.2636926769</v>
+        <v>546835</v>
       </c>
       <c r="R2" t="n">
-        <v>6269333.217846672</v>
+        <v>6269333</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74464580</v>
       </c>
       <c r="B3" t="n">
-        <v>101692</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546835.2636926769</v>
+        <v>546835</v>
       </c>
       <c r="R3" t="n">
-        <v>6269333.217846672</v>
+        <v>6269333</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -870,19 +850,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -926,12 +896,7 @@
         <v>74770982</v>
       </c>
       <c r="B4" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546835.2636926769</v>
+        <v>546835</v>
       </c>
       <c r="R4" t="n">
-        <v>6269333.217846672</v>
+        <v>6269333</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -996,19 +961,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 59457-2023 artfynd.xlsx
+++ b/artfynd/A 59457-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74209838</v>
       </c>
       <c r="B2" t="n">
-        <v>99215</v>
+        <v>99220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74464580</v>
       </c>
       <c r="B3" t="n">
-        <v>104061</v>
+        <v>104070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74770982</v>
       </c>
       <c r="B4" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2023 artfynd.xlsx
+++ b/artfynd/A 59457-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74209838</v>
       </c>
       <c r="B2" t="n">
-        <v>99220</v>
+        <v>99221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74464580</v>
       </c>
       <c r="B3" t="n">
-        <v>104070</v>
+        <v>104073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74770982</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2023 artfynd.xlsx
+++ b/artfynd/A 59457-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74209838</v>
       </c>
       <c r="B2" t="n">
-        <v>99221</v>
+        <v>99248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74464580</v>
       </c>
       <c r="B3" t="n">
-        <v>104073</v>
+        <v>104100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74770982</v>
       </c>
       <c r="B4" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2023 artfynd.xlsx
+++ b/artfynd/A 59457-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74209838</v>
       </c>
       <c r="B2" t="n">
-        <v>99248</v>
+        <v>99254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74464580</v>
       </c>
       <c r="B3" t="n">
-        <v>104100</v>
+        <v>104106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74770982</v>
       </c>
       <c r="B4" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2023 artfynd.xlsx
+++ b/artfynd/A 59457-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74209838</v>
       </c>
       <c r="B2" t="n">
-        <v>99254</v>
+        <v>99261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74464580</v>
       </c>
       <c r="B3" t="n">
-        <v>104106</v>
+        <v>104113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74770982</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2023 artfynd.xlsx
+++ b/artfynd/A 59457-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74209838</v>
       </c>
       <c r="B2" t="n">
-        <v>99261</v>
+        <v>99265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74464580</v>
       </c>
       <c r="B3" t="n">
-        <v>104113</v>
+        <v>104117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74770982</v>
       </c>
       <c r="B4" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2023 artfynd.xlsx
+++ b/artfynd/A 59457-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74209838</v>
       </c>
       <c r="B2" t="n">
-        <v>99265</v>
+        <v>99272</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74464580</v>
       </c>
       <c r="B3" t="n">
-        <v>104117</v>
+        <v>104124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74770982</v>
       </c>
       <c r="B4" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2023 artfynd.xlsx
+++ b/artfynd/A 59457-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74209838</v>
       </c>
       <c r="B2" t="n">
-        <v>99275</v>
+        <v>99280</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74464580</v>
       </c>
       <c r="B3" t="n">
-        <v>104127</v>
+        <v>104132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74770982</v>
       </c>
       <c r="B4" t="n">
-        <v>98680</v>
+        <v>98685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2023 artfynd.xlsx
+++ b/artfynd/A 59457-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74209838</v>
       </c>
       <c r="B2" t="n">
-        <v>99280</v>
+        <v>99288</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74464580</v>
       </c>
       <c r="B3" t="n">
-        <v>104132</v>
+        <v>104140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74770982</v>
       </c>
       <c r="B4" t="n">
-        <v>98685</v>
+        <v>98693</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2023 artfynd.xlsx
+++ b/artfynd/A 59457-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74209838</v>
       </c>
       <c r="B2" t="n">
-        <v>99288</v>
+        <v>99298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74464580</v>
       </c>
       <c r="B3" t="n">
-        <v>104140</v>
+        <v>104150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74770982</v>
       </c>
       <c r="B4" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2023 artfynd.xlsx
+++ b/artfynd/A 59457-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74209838</v>
+        <v>74770982</v>
       </c>
       <c r="B2" t="n">
-        <v>99298</v>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222295</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4F4j 0923. SOM: Carex caryophyllea. LEG: Per Hartvig</t>
+          <t>Smålands flora 2007: KOO: 4F4j 0923. SOM: Platanthera bifolia. LEG: Per Hartvig</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74464580</v>
+        <v>74784376</v>
       </c>
       <c r="B3" t="n">
-        <v>104150</v>
+        <v>102559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,19 +797,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224416</v>
+        <v>222133</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -857,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4F4j 0923. SOM: Helianthemum nummularium ssp. nummularium. LEG: Per Hartvig</t>
+          <t>Smålands flora 2007: KOO: 4F4j 0923. SOM: Polygala vulgaris. LEG: Per Hartvig</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74770982</v>
+        <v>74209838</v>
       </c>
       <c r="B4" t="n">
-        <v>98703</v>
+        <v>99754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>222295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -968,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4F4j 0923. SOM: Platanthera bifolia. LEG: Per Hartvig</t>
+          <t>Smålands flora 2007: KOO: 4F4j 0923. SOM: Carex caryophyllea. LEG: Per Hartvig</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,6 +1001,113 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>74464580</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>L3 Träkniv östra gdn 400 m VNV t V, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>546835</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6269333</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlslunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1989-01-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1989-12-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 4F4j 0923. SOM: Helianthemum nummularium ssp. nummularium. LEG: Per Hartvig</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Hagmark - torräng</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 59457-2023 artfynd.xlsx
+++ b/artfynd/A 59457-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74770982</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74784376</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74209838</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,8 +1132,19 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74464580</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>